--- a/CG-loc.xlsx
+++ b/CG-loc.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03820908-BB56-4EC1-B056-6FB99D5FCEB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" xr2:uid="{F654CED2-9492-4B18-8D31-DA0C42F03B2A}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F654CED2-9492-4B18-8D31-DA0C42F03B2A}"/>
   </bookViews>
   <sheets>
     <sheet name="CG Full payload + Full Fuel" sheetId="1" r:id="rId1"/>
